--- a/results/Int Task Remove ACC -0.2/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_7_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6778765912632182</v>
+        <v>0.6760160373465705</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7049144654320456</v>
+        <v>0.7058409445036367</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7061747479537601</v>
+        <v>0.7272501452435061</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7061747479537601</v>
+        <v>0.749801586079616</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7055059093064648</v>
+        <v>0.7500452667040296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7100900612383574</v>
+        <v>0.7465690712421964</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7100900612383574</v>
+        <v>0.7446463140996031</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7391053000022583</v>
+        <v>0.7455169539716657</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7511228400802278</v>
+        <v>0.7484220293853787</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7531991550215248</v>
+        <v>0.7510897882010951</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7531991550215248</v>
+        <v>0.7731259481886132</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7743355237901678</v>
+        <v>0.7627240496558294</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7793029543452956</v>
+        <v>0.7540075916676419</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7731856879204619</v>
+        <v>0.7601172623190102</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7596210735496691</v>
+        <v>0.7696548850061484</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7620108681147906</v>
+        <v>0.7633776967561942</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.762324347738615</v>
+        <v>0.7874965357114263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7606731908201998</v>
+        <v>0.7832398232032403</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7578937536054262</v>
+        <v>0.7940174045857942</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7545990355420611</v>
+        <v>0.8014850763580524</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7143835208668214</v>
+        <v>0.7830786696310712</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7218448286126627</v>
+        <v>0.7954731243058593</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7267145405686155</v>
+        <v>0.7954731243058593</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7314040068731484</v>
+        <v>0.7884636624356156</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7221734997834178</v>
+        <v>0.7852590671979602</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7196098235932935</v>
+        <v>0.7852590671979602</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7344207606859189</v>
+        <v>0.8135711836883843</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7340933212622123</v>
+        <v>0.8142121027359155</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7340933212622123</v>
+        <v>0.8239870420210506</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7126219172963973</v>
+        <v>0.8251368778907564</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7484181288530587</v>
+        <v>0.8106876638480189</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7478418765255701</v>
+        <v>0.8116281027194923</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7411738138789152</v>
+        <v>0.7950834816562071</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7717679470677234</v>
+        <v>0.7465310923748698</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7228969458831934</v>
+        <v>0.7465310923748698</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6973236189549448</v>
+        <v>0.7365479878385508</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.613898623112091</v>
+        <v>0.7368754272622574</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.651706482890007</v>
+        <v>0.7318254696548849</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6551902741253056</v>
+        <v>0.731184550607354</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6492468893254748</v>
+        <v>0.7214933701215118</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6060185213697848</v>
+        <v>0.6777103054116806</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6106496849806924</v>
+        <v>0.681911178720338</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6119594426755188</v>
+        <v>0.6772724193359652</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6109555688310515</v>
+        <v>0.6657067251335933</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6622290926335368</v>
+        <v>0.6657067251335933</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6697944830049701</v>
+        <v>0.7051823704150781</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6429456820080761</v>
+        <v>0.6459221987505979</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6417336429124249</v>
+        <v>0.6599678103438011</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6408071638408337</v>
+        <v>0.6599678103438011</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6408071638408337</v>
+        <v>0.6515736594999517</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5959795776339371</v>
+        <v>0.6530928141930107</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5950112191626994</v>
+        <v>0.6637739087234379</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5606413706881155</v>
+        <v>0.6647143475949113</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5811723357824571</v>
+        <v>0.6737557815127085</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5921671152278835</v>
+        <v>0.6634376417792176</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.588288754354739</v>
+        <v>0.6567492553062637</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5708962807397873</v>
+        <v>0.666676520643054</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5725753572579668</v>
+        <v>0.6673034798907029</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5744701948007958</v>
+        <v>0.7252220737282725</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6278773097823298</v>
+        <v>0.7030996914473644</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6160196915294809</v>
+        <v>0.6694762816841267</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5943440228448019</v>
+        <v>0.6653642994541308</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5933477447737999</v>
+        <v>0.6627092686912482</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.517371944497478</v>
+        <v>0.6832047184123602</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5107812766236992</v>
+        <v>0.6986107946205501</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5178453459464231</v>
+        <v>0.701954987857027</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5054788108713995</v>
+        <v>0.7053207366668515</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5041208097505097</v>
+        <v>0.7326885137534822</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5113712834598954</v>
+        <v>0.7222523315945171</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5020785731442191</v>
+        <v>0.7126588697078502</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5013869471765278</v>
+        <v>0.6518224724037338</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4972813289729487</v>
+        <v>0.6499808052751621</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4959576114782401</v>
+        <v>0.6449727270674361</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4996774875644871</v>
+        <v>0.6528947082093888</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4993640079406627</v>
+        <v>0.6528947082093888</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4938533769371788</v>
+        <v>0.5658949771408277</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4943546979858883</v>
+        <v>0.5424640689121415</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.491895104421356</v>
+        <v>0.5589413544701127</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4747945548568813</v>
+        <v>0.5612346621831075</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5082949952064511</v>
+        <v>0.5654585281033353</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5057528745896743</v>
+        <v>0.5654585281033353</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5087314442439433</v>
+        <v>0.5805347013937218</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4853208598415563</v>
+        <v>0.5723144321748752</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4880799732300308</v>
+        <v>0.5650497933744326</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4871231110645785</v>
+        <v>0.5067023462728361</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4864758279906305</v>
+        <v>0.5061172664248337</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4775867201244886</v>
+        <v>0.5061172664248337</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4889569771285102</v>
+        <v>0.5060753870251872</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4986760772141167</v>
+        <v>0.5029964299864713</v>
       </c>
     </row>
   </sheetData>
